--- a/server/api/offshore_forecast_api/models/topside_production_feature_importance.xlsx
+++ b/server/api/offshore_forecast_api/models/topside_production_feature_importance.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6605258584022522</v>
+        <v>0.5805057287216187</v>
       </c>
       <c r="C2" t="n">
-        <v>66.05258941650391</v>
+        <v>58.05057144165039</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3394741714000702</v>
+        <v>0.4194942712783813</v>
       </c>
       <c r="C3" t="n">
-        <v>33.94741821289062</v>
+        <v>41.94942855834961</v>
       </c>
     </row>
   </sheetData>
